--- a/public/templates/process-docs/综合楼光伏组件安装分项工程质量验收表.xlsx
+++ b/public/templates/process-docs/综合楼光伏组件安装分项工程质量验收表.xlsx
@@ -104,7 +104,7 @@
         <rFont val="宋体"/>
         <family val="0"/>
       </rPr>
-      <t xml:space="preserve">5028G01-SG-ZHHC-01-01-10-001</t>
+      <t xml:space="preserve">{{文件编号}}</t>
     </r>
   </si>
   <si>
